--- a/labyItems/Resources/Raw/people/NonPowerUser.xlsx
+++ b/labyItems/Resources/Raw/people/NonPowerUser.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brbar/Source/labyItems/labyItems/Resources/Raw/people/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660178CF-FD18-DC49-A161-094D0A2DC3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FBD993-6609-904E-8591-6C2D4135A6AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -944,39 +944,82 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -989,89 +1032,46 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1318,73 +1318,73 @@
   <sheetData>
     <row r="1" spans="1:32" ht="22.5" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="78"/>
+      <c r="Y1" s="78"/>
+      <c r="Z1" s="78"/>
+      <c r="AA1" s="78"/>
+      <c r="AB1" s="78"/>
+      <c r="AC1" s="78"/>
+      <c r="AD1" s="78"/>
       <c r="AE1" s="2"/>
       <c r="AF1" s="3"/>
     </row>
     <row r="2" spans="1:32" ht="45.75" customHeight="1">
       <c r="A2" s="4"/>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="53"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="53"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="76"/>
+      <c r="Z2" s="76"/>
+      <c r="AA2" s="76"/>
+      <c r="AB2" s="76"/>
+      <c r="AC2" s="76"/>
+      <c r="AD2" s="76"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="6"/>
     </row>
@@ -1394,21 +1394,21 @@
         <v>2</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="68"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="59"/>
       <c r="M3" s="10"/>
-      <c r="N3" s="88" t="s">
+      <c r="N3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="85"/>
-      <c r="P3" s="89"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="83"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="10"/>
@@ -1418,8 +1418,8 @@
       <c r="U3" s="12"/>
       <c r="V3" s="11"/>
       <c r="W3" s="13"/>
-      <c r="X3" s="83"/>
-      <c r="Y3" s="67"/>
+      <c r="X3" s="74"/>
+      <c r="Y3" s="58"/>
       <c r="Z3" s="14"/>
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
@@ -1435,21 +1435,21 @@
     </row>
     <row r="4" spans="1:32" ht="13.5" customHeight="1">
       <c r="A4" s="7"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="59"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="69"/>
       <c r="M4" s="10"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="62"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="55"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
@@ -1458,10 +1458,10 @@
       </c>
       <c r="U4" s="18"/>
       <c r="V4" s="11"/>
-      <c r="W4" s="57"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="59"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="68"/>
+      <c r="Y4" s="68"/>
+      <c r="Z4" s="69"/>
       <c r="AA4" s="10"/>
       <c r="AB4" s="10"/>
       <c r="AC4" s="15"/>
@@ -1471,21 +1471,21 @@
     </row>
     <row r="5" spans="1:32" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="62"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="55"/>
       <c r="M5" s="10"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="61"/>
-      <c r="P5" s="62"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="55"/>
       <c r="Q5" s="10"/>
       <c r="S5" s="10"/>
       <c r="T5" s="11" t="s">
@@ -1493,10 +1493,10 @@
       </c>
       <c r="U5" s="18"/>
       <c r="V5" s="11"/>
-      <c r="W5" s="60"/>
-      <c r="X5" s="61"/>
-      <c r="Y5" s="61"/>
-      <c r="Z5" s="62"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="54"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="55"/>
       <c r="AA5" s="10"/>
       <c r="AB5" s="10"/>
       <c r="AC5" s="19"/>
@@ -1506,21 +1506,21 @@
     </row>
     <row r="6" spans="1:32" ht="13.5" customHeight="1">
       <c r="A6" s="7"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="62"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
       <c r="M6" s="10"/>
-      <c r="N6" s="81"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="62"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="55"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
@@ -1529,10 +1529,10 @@
       </c>
       <c r="U6" s="18"/>
       <c r="V6" s="11"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="61"/>
-      <c r="Z6" s="62"/>
+      <c r="W6" s="65"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="55"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="10"/>
       <c r="AC6" s="20"/>
@@ -1542,69 +1542,69 @@
     </row>
     <row r="7" spans="1:32" ht="13.5" customHeight="1">
       <c r="A7" s="7"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="62"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="55"/>
       <c r="M7" s="10"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="62"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="55"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
-      <c r="S7" s="54" t="s">
+      <c r="S7" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="63"/>
-      <c r="X7" s="64"/>
-      <c r="Y7" s="64"/>
-      <c r="Z7" s="65"/>
-      <c r="AA7" s="86" t="s">
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="66"/>
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="63"/>
+      <c r="AA7" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="AB7" s="55"/>
-      <c r="AC7" s="55"/>
-      <c r="AD7" s="55"/>
+      <c r="AB7" s="51"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="51"/>
       <c r="AE7" s="16"/>
       <c r="AF7" s="3"/>
     </row>
     <row r="8" spans="1:32" ht="13.5" customHeight="1">
       <c r="A8" s="7"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="62"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
       <c r="M8" s="10"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="61"/>
-      <c r="P8" s="62"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="55"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="13"/>
       <c r="T8" s="13"/>
       <c r="U8" s="13"/>
       <c r="V8" s="13"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="67"/>
-      <c r="Z8" s="67"/>
+      <c r="W8" s="74"/>
+      <c r="X8" s="58"/>
+      <c r="Y8" s="58"/>
+      <c r="Z8" s="58"/>
       <c r="AA8" s="23"/>
       <c r="AB8" s="13"/>
       <c r="AC8" s="24"/>
@@ -1614,276 +1614,276 @@
     </row>
     <row r="9" spans="1:32" ht="12.75" customHeight="1">
       <c r="A9" s="7"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="62"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="55"/>
       <c r="M9" s="10"/>
-      <c r="N9" s="81"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="62"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="55"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
-      <c r="S9" s="57"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="57"/>
-      <c r="W9" s="58"/>
-      <c r="X9" s="58"/>
-      <c r="Y9" s="58"/>
-      <c r="Z9" s="58"/>
-      <c r="AA9" s="59"/>
-      <c r="AB9" s="57"/>
-      <c r="AC9" s="58"/>
-      <c r="AD9" s="59"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="68"/>
+      <c r="U9" s="69"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="68"/>
+      <c r="X9" s="68"/>
+      <c r="Y9" s="68"/>
+      <c r="Z9" s="68"/>
+      <c r="AA9" s="69"/>
+      <c r="AB9" s="67"/>
+      <c r="AC9" s="68"/>
+      <c r="AD9" s="69"/>
       <c r="AE9" s="16"/>
       <c r="AF9" s="3"/>
     </row>
     <row r="10" spans="1:32" ht="12.75" customHeight="1">
       <c r="A10" s="7"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="61"/>
-      <c r="I10" s="61"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="62"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="55"/>
       <c r="M10" s="10"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="61"/>
-      <c r="P10" s="62"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="55"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
-      <c r="S10" s="60"/>
-      <c r="T10" s="61"/>
-      <c r="U10" s="62"/>
-      <c r="V10" s="60"/>
-      <c r="W10" s="61"/>
-      <c r="X10" s="61"/>
-      <c r="Y10" s="61"/>
-      <c r="Z10" s="61"/>
-      <c r="AA10" s="62"/>
-      <c r="AB10" s="60"/>
-      <c r="AC10" s="61"/>
-      <c r="AD10" s="62"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="55"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="55"/>
       <c r="AE10" s="16"/>
       <c r="AF10" s="3"/>
     </row>
     <row r="11" spans="1:32" ht="12.75" customHeight="1">
       <c r="A11" s="7"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
       <c r="M11" s="10"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="61"/>
-      <c r="P11" s="62"/>
+      <c r="N11" s="53"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="55"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="61"/>
-      <c r="U11" s="62"/>
-      <c r="V11" s="60"/>
-      <c r="W11" s="61"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="61"/>
-      <c r="Z11" s="61"/>
-      <c r="AA11" s="62"/>
-      <c r="AB11" s="60"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="62"/>
+      <c r="S11" s="65"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="55"/>
       <c r="AE11" s="16"/>
       <c r="AF11" s="3"/>
     </row>
     <row r="12" spans="1:32" ht="12.75" customHeight="1">
       <c r="A12" s="7"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="61"/>
-      <c r="P12" s="62"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="55"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
-      <c r="S12" s="60"/>
-      <c r="T12" s="61"/>
-      <c r="U12" s="62"/>
-      <c r="V12" s="60"/>
-      <c r="W12" s="61"/>
-      <c r="X12" s="61"/>
-      <c r="Y12" s="61"/>
-      <c r="Z12" s="61"/>
-      <c r="AA12" s="62"/>
-      <c r="AB12" s="60"/>
-      <c r="AC12" s="61"/>
-      <c r="AD12" s="62"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="55"/>
       <c r="AE12" s="16"/>
       <c r="AF12" s="3"/>
     </row>
     <row r="13" spans="1:32" ht="12.75" customHeight="1">
       <c r="A13" s="7"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="62"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
       <c r="M13" s="10"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="62"/>
+      <c r="N13" s="53"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="55"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="61"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="61"/>
-      <c r="X13" s="61"/>
-      <c r="Y13" s="61"/>
-      <c r="Z13" s="61"/>
-      <c r="AA13" s="62"/>
-      <c r="AB13" s="60"/>
-      <c r="AC13" s="61"/>
-      <c r="AD13" s="62"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="55"/>
       <c r="AE13" s="16"/>
       <c r="AF13" s="3"/>
     </row>
     <row r="14" spans="1:32" ht="12.75" customHeight="1">
       <c r="A14" s="7"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="62"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="61"/>
-      <c r="P14" s="62"/>
+      <c r="N14" s="53"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="55"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="61"/>
-      <c r="U14" s="62"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="61"/>
-      <c r="X14" s="61"/>
-      <c r="Y14" s="61"/>
-      <c r="Z14" s="61"/>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="61"/>
-      <c r="AD14" s="62"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="55"/>
       <c r="AE14" s="16"/>
       <c r="AF14" s="3"/>
     </row>
     <row r="15" spans="1:32" ht="13.5" customHeight="1">
       <c r="A15" s="7"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="64"/>
-      <c r="L15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
       <c r="M15" s="10"/>
-      <c r="N15" s="81"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="62"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="55"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="61"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="61"/>
-      <c r="Z15" s="61"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="61"/>
-      <c r="AD15" s="62"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="55"/>
+      <c r="V15" s="65"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="55"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="55"/>
       <c r="AE15" s="16"/>
       <c r="AF15" s="3"/>
     </row>
     <row r="16" spans="1:32" ht="13.5" customHeight="1">
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="54" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
       <c r="M16" s="10"/>
-      <c r="N16" s="81"/>
-      <c r="O16" s="61"/>
-      <c r="P16" s="62"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="55"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="61"/>
-      <c r="U16" s="62"/>
-      <c r="V16" s="63"/>
-      <c r="W16" s="64"/>
-      <c r="X16" s="64"/>
-      <c r="Y16" s="64"/>
-      <c r="Z16" s="64"/>
-      <c r="AA16" s="65"/>
-      <c r="AB16" s="60"/>
-      <c r="AC16" s="61"/>
-      <c r="AD16" s="62"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="55"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="62"/>
+      <c r="X16" s="62"/>
+      <c r="Y16" s="62"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="63"/>
+      <c r="AB16" s="65"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="55"/>
       <c r="AE16" s="16"/>
       <c r="AF16" s="3"/>
     </row>
@@ -1891,9 +1891,9 @@
       <c r="A17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="68"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="59"/>
       <c r="E17" s="26">
         <v>1</v>
       </c>
@@ -1919,25 +1919,25 @@
         <v>8</v>
       </c>
       <c r="M17" s="10"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="61"/>
-      <c r="P17" s="62"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="55"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="61"/>
-      <c r="U17" s="62"/>
+      <c r="S17" s="65"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="55"/>
       <c r="V17" s="13">
         <v>15</v>
       </c>
-      <c r="W17" s="83"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="67"/>
+      <c r="W17" s="74"/>
+      <c r="X17" s="58"/>
+      <c r="Y17" s="58"/>
+      <c r="Z17" s="58"/>
       <c r="AA17" s="23"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="61"/>
-      <c r="AD17" s="62"/>
+      <c r="AB17" s="65"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="55"/>
       <c r="AE17" s="16"/>
       <c r="AF17" s="3"/>
     </row>
@@ -1945,9 +1945,9 @@
       <c r="A18" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="80"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="62"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="29">
         <v>1</v>
       </c>
@@ -1973,33 +1973,33 @@
         <v>8</v>
       </c>
       <c r="M18" s="10"/>
-      <c r="N18" s="81" t="s">
+      <c r="N18" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O18" s="61"/>
-      <c r="P18" s="62"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="55"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
-      <c r="S18" s="63"/>
-      <c r="T18" s="64"/>
-      <c r="U18" s="65"/>
-      <c r="V18" s="57"/>
-      <c r="W18" s="58"/>
-      <c r="X18" s="58"/>
-      <c r="Y18" s="58"/>
-      <c r="Z18" s="58"/>
-      <c r="AA18" s="59"/>
-      <c r="AB18" s="63"/>
-      <c r="AC18" s="64"/>
-      <c r="AD18" s="65"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="63"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="68"/>
+      <c r="X18" s="68"/>
+      <c r="Y18" s="68"/>
+      <c r="Z18" s="68"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="66"/>
+      <c r="AC18" s="62"/>
+      <c r="AD18" s="63"/>
       <c r="AE18" s="16"/>
       <c r="AF18" s="3"/>
     </row>
     <row r="19" spans="1:32" ht="13.5" customHeight="1">
       <c r="A19" s="28"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="62"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="55"/>
       <c r="E19" s="29">
         <v>1</v>
       </c>
@@ -2025,37 +2025,37 @@
         <v>8</v>
       </c>
       <c r="M19" s="10"/>
-      <c r="N19" s="81" t="s">
+      <c r="N19" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O19" s="61"/>
-      <c r="P19" s="62"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="55"/>
       <c r="Q19" s="10"/>
-      <c r="R19" s="52" t="s">
+      <c r="R19" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="S19" s="53"/>
-      <c r="T19" s="53"/>
+      <c r="S19" s="76"/>
+      <c r="T19" s="76"/>
       <c r="U19" s="32"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="61"/>
-      <c r="X19" s="61"/>
-      <c r="Y19" s="61"/>
-      <c r="Z19" s="61"/>
-      <c r="AA19" s="62"/>
-      <c r="AB19" s="88" t="s">
+      <c r="V19" s="65"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="55"/>
+      <c r="AB19" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="AC19" s="85"/>
-      <c r="AD19" s="85"/>
+      <c r="AC19" s="78"/>
+      <c r="AD19" s="78"/>
       <c r="AE19" s="16"/>
       <c r="AF19" s="3"/>
     </row>
     <row r="20" spans="1:32" ht="13.5" customHeight="1">
       <c r="A20" s="28"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="62"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="29">
         <v>1</v>
       </c>
@@ -2081,24 +2081,24 @@
         <v>8</v>
       </c>
       <c r="M20" s="10"/>
-      <c r="N20" s="81" t="s">
+      <c r="N20" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O20" s="61"/>
-      <c r="P20" s="62"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="55"/>
       <c r="Q20" s="10"/>
-      <c r="R20" s="66" t="s">
+      <c r="R20" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="S20" s="67"/>
-      <c r="T20" s="68"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="59"/>
       <c r="U20" s="10"/>
-      <c r="V20" s="60"/>
-      <c r="W20" s="61"/>
-      <c r="X20" s="61"/>
-      <c r="Y20" s="61"/>
-      <c r="Z20" s="61"/>
-      <c r="AA20" s="62"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="54"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="55"/>
       <c r="AB20" s="10"/>
       <c r="AC20" s="15" t="s">
         <v>15</v>
@@ -2109,9 +2109,9 @@
     </row>
     <row r="21" spans="1:32" ht="12.75" customHeight="1">
       <c r="A21" s="28"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="62"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
       <c r="E21" s="29">
         <v>1</v>
       </c>
@@ -2137,24 +2137,24 @@
         <v>8</v>
       </c>
       <c r="M21" s="10"/>
-      <c r="N21" s="81" t="s">
+      <c r="N21" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O21" s="61"/>
-      <c r="P21" s="62"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="55"/>
       <c r="Q21" s="10"/>
-      <c r="R21" s="69" t="s">
+      <c r="R21" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S21" s="58"/>
-      <c r="T21" s="59"/>
+      <c r="S21" s="68"/>
+      <c r="T21" s="69"/>
       <c r="U21" s="10"/>
-      <c r="V21" s="60"/>
-      <c r="W21" s="61"/>
-      <c r="X21" s="61"/>
-      <c r="Y21" s="61"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="62"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="54"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="55"/>
       <c r="AB21" s="10"/>
       <c r="AC21" s="15" t="s">
         <v>16</v>
@@ -2165,9 +2165,9 @@
     </row>
     <row r="22" spans="1:32" ht="12.75" customHeight="1">
       <c r="A22" s="28"/>
-      <c r="B22" s="80"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="62"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="55"/>
       <c r="E22" s="29">
         <v>1</v>
       </c>
@@ -2193,24 +2193,24 @@
         <v>8</v>
       </c>
       <c r="M22" s="10"/>
-      <c r="N22" s="81" t="s">
+      <c r="N22" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O22" s="61"/>
-      <c r="P22" s="62"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="55"/>
       <c r="Q22" s="10"/>
-      <c r="R22" s="69" t="s">
+      <c r="R22" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S22" s="58"/>
-      <c r="T22" s="59"/>
+      <c r="S22" s="68"/>
+      <c r="T22" s="69"/>
       <c r="U22" s="10"/>
-      <c r="V22" s="60"/>
-      <c r="W22" s="61"/>
-      <c r="X22" s="61"/>
-      <c r="Y22" s="61"/>
-      <c r="Z22" s="61"/>
-      <c r="AA22" s="62"/>
+      <c r="V22" s="65"/>
+      <c r="W22" s="54"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="55"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="15" t="s">
         <v>17</v>
@@ -2221,9 +2221,9 @@
     </row>
     <row r="23" spans="1:32" ht="12.75" customHeight="1">
       <c r="A23" s="28"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="29">
         <v>1</v>
       </c>
@@ -2249,24 +2249,24 @@
         <v>8</v>
       </c>
       <c r="M23" s="10"/>
-      <c r="N23" s="81" t="s">
+      <c r="N23" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O23" s="61"/>
-      <c r="P23" s="62"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="55"/>
       <c r="Q23" s="10"/>
-      <c r="R23" s="69" t="s">
+      <c r="R23" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S23" s="58"/>
-      <c r="T23" s="59"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="69"/>
       <c r="U23" s="10"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="61"/>
-      <c r="Y23" s="61"/>
-      <c r="Z23" s="61"/>
-      <c r="AA23" s="62"/>
+      <c r="V23" s="65"/>
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="55"/>
       <c r="AB23" s="10"/>
       <c r="AC23" s="15" t="s">
         <v>18</v>
@@ -2277,9 +2277,9 @@
     </row>
     <row r="24" spans="1:32" ht="13.5" customHeight="1">
       <c r="A24" s="28"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="62"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="29">
         <v>1</v>
       </c>
@@ -2305,33 +2305,33 @@
         <v>8</v>
       </c>
       <c r="M24" s="10"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O24" s="61"/>
-      <c r="P24" s="62"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="55"/>
       <c r="Q24" s="10"/>
-      <c r="R24" s="69" t="s">
+      <c r="R24" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S24" s="58"/>
-      <c r="T24" s="59"/>
+      <c r="S24" s="68"/>
+      <c r="T24" s="69"/>
       <c r="U24" s="10"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64"/>
-      <c r="Z24" s="64"/>
-      <c r="AA24" s="65"/>
+      <c r="V24" s="66"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="62"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="62"/>
+      <c r="AA24" s="63"/>
       <c r="AB24" s="10"/>
       <c r="AE24" s="16"/>
       <c r="AF24" s="3"/>
     </row>
     <row r="25" spans="1:32" ht="13.5" customHeight="1">
       <c r="A25" s="28"/>
-      <c r="B25" s="80"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="62"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="55"/>
       <c r="E25" s="29">
         <v>1</v>
       </c>
@@ -2357,17 +2357,17 @@
         <v>8</v>
       </c>
       <c r="M25" s="10"/>
-      <c r="N25" s="81" t="s">
+      <c r="N25" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O25" s="61"/>
-      <c r="P25" s="62"/>
+      <c r="O25" s="54"/>
+      <c r="P25" s="55"/>
       <c r="Q25" s="10"/>
-      <c r="R25" s="69" t="s">
+      <c r="R25" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S25" s="58"/>
-      <c r="T25" s="59"/>
+      <c r="S25" s="68"/>
+      <c r="T25" s="69"/>
       <c r="U25" s="10"/>
       <c r="V25" s="13"/>
       <c r="W25" s="24"/>
@@ -2376,18 +2376,18 @@
       <c r="Z25" s="24"/>
       <c r="AA25" s="24"/>
       <c r="AB25" s="10"/>
-      <c r="AC25" s="96" t="s">
+      <c r="AC25" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="AD25" s="68"/>
+      <c r="AD25" s="59"/>
       <c r="AE25" s="16"/>
       <c r="AF25" s="3"/>
     </row>
     <row r="26" spans="1:32" ht="13.5" customHeight="1">
       <c r="A26" s="28"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="61"/>
-      <c r="D26" s="62"/>
+      <c r="B26" s="84"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="55"/>
       <c r="E26" s="29">
         <v>1</v>
       </c>
@@ -2413,34 +2413,34 @@
         <v>8</v>
       </c>
       <c r="M26" s="10"/>
-      <c r="N26" s="81" t="s">
+      <c r="N26" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O26" s="61"/>
-      <c r="P26" s="62"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="55"/>
       <c r="Q26" s="10"/>
-      <c r="R26" s="69" t="s">
+      <c r="R26" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S26" s="58"/>
-      <c r="T26" s="59"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="69"/>
       <c r="U26" s="10"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="59"/>
-      <c r="Y26" s="57"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="59"/>
-      <c r="AC26" s="97"/>
-      <c r="AD26" s="59"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="69"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="68"/>
+      <c r="AA26" s="69"/>
+      <c r="AC26" s="71"/>
+      <c r="AD26" s="69"/>
       <c r="AE26" s="16"/>
       <c r="AF26" s="3"/>
     </row>
     <row r="27" spans="1:32" ht="12.75" customHeight="1">
       <c r="A27" s="28"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="61"/>
-      <c r="D27" s="62"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="55"/>
       <c r="E27" s="29">
         <v>1</v>
       </c>
@@ -2466,37 +2466,37 @@
         <v>8</v>
       </c>
       <c r="M27" s="10"/>
-      <c r="N27" s="81" t="s">
+      <c r="N27" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O27" s="61"/>
-      <c r="P27" s="62"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="55"/>
       <c r="Q27" s="10"/>
-      <c r="R27" s="69" t="s">
+      <c r="R27" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S27" s="58"/>
-      <c r="T27" s="59"/>
+      <c r="S27" s="68"/>
+      <c r="T27" s="69"/>
       <c r="U27" s="10"/>
-      <c r="V27" s="60"/>
-      <c r="W27" s="61"/>
-      <c r="X27" s="62"/>
-      <c r="Y27" s="60"/>
-      <c r="Z27" s="61"/>
-      <c r="AA27" s="62"/>
+      <c r="V27" s="65"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="55"/>
+      <c r="Y27" s="65"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="55"/>
       <c r="AB27" s="33"/>
-      <c r="AC27" s="90" t="s">
+      <c r="AC27" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD27" s="59"/>
+      <c r="AD27" s="69"/>
       <c r="AE27" s="16"/>
       <c r="AF27" s="3"/>
     </row>
     <row r="28" spans="1:32" ht="12.75" customHeight="1">
       <c r="A28" s="28"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="62"/>
+      <c r="B28" s="84"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="55"/>
       <c r="E28" s="29">
         <v>1</v>
       </c>
@@ -2522,37 +2522,37 @@
         <v>8</v>
       </c>
       <c r="M28" s="10"/>
-      <c r="N28" s="81" t="s">
+      <c r="N28" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O28" s="61"/>
-      <c r="P28" s="62"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="55"/>
       <c r="Q28" s="10"/>
-      <c r="R28" s="69" t="s">
+      <c r="R28" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S28" s="58"/>
-      <c r="T28" s="59"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="69"/>
       <c r="U28" s="10"/>
-      <c r="V28" s="60"/>
-      <c r="W28" s="61"/>
-      <c r="X28" s="62"/>
-      <c r="Y28" s="60"/>
-      <c r="Z28" s="61"/>
-      <c r="AA28" s="62"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="54"/>
+      <c r="X28" s="55"/>
+      <c r="Y28" s="65"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="55"/>
       <c r="AB28" s="33"/>
-      <c r="AC28" s="90" t="s">
+      <c r="AC28" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD28" s="59"/>
+      <c r="AD28" s="69"/>
       <c r="AE28" s="16"/>
       <c r="AF28" s="3"/>
     </row>
     <row r="29" spans="1:32" ht="12.75" customHeight="1">
       <c r="A29" s="28"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="62"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="55"/>
       <c r="E29" s="29">
         <v>1</v>
       </c>
@@ -2578,37 +2578,37 @@
         <v>8</v>
       </c>
       <c r="M29" s="10"/>
-      <c r="N29" s="81" t="s">
+      <c r="N29" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O29" s="61"/>
-      <c r="P29" s="62"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="55"/>
       <c r="Q29" s="10"/>
-      <c r="R29" s="69" t="s">
+      <c r="R29" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S29" s="58"/>
-      <c r="T29" s="59"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="69"/>
       <c r="U29" s="10"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="61"/>
-      <c r="X29" s="62"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="61"/>
-      <c r="AA29" s="62"/>
+      <c r="V29" s="65"/>
+      <c r="W29" s="54"/>
+      <c r="X29" s="55"/>
+      <c r="Y29" s="65"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="55"/>
       <c r="AB29" s="33"/>
-      <c r="AC29" s="90" t="s">
+      <c r="AC29" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD29" s="59"/>
+      <c r="AD29" s="69"/>
       <c r="AE29" s="16"/>
       <c r="AF29" s="3"/>
     </row>
     <row r="30" spans="1:32" ht="12.75" customHeight="1">
       <c r="A30" s="28"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="62"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="55"/>
       <c r="E30" s="29">
         <v>1</v>
       </c>
@@ -2634,37 +2634,37 @@
         <v>8</v>
       </c>
       <c r="M30" s="10"/>
-      <c r="N30" s="81" t="s">
+      <c r="N30" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O30" s="61"/>
-      <c r="P30" s="62"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="55"/>
       <c r="Q30" s="10"/>
-      <c r="R30" s="69" t="s">
+      <c r="R30" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S30" s="58"/>
-      <c r="T30" s="59"/>
+      <c r="S30" s="68"/>
+      <c r="T30" s="69"/>
       <c r="U30" s="10"/>
-      <c r="V30" s="60"/>
-      <c r="W30" s="61"/>
-      <c r="X30" s="62"/>
-      <c r="Y30" s="60"/>
-      <c r="Z30" s="61"/>
-      <c r="AA30" s="62"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="55"/>
+      <c r="Y30" s="65"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="55"/>
       <c r="AB30" s="33"/>
-      <c r="AC30" s="90" t="s">
+      <c r="AC30" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD30" s="59"/>
+      <c r="AD30" s="69"/>
       <c r="AE30" s="16"/>
       <c r="AF30" s="3"/>
     </row>
     <row r="31" spans="1:32" ht="12.75" customHeight="1">
       <c r="A31" s="28"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="62"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="29">
         <v>1</v>
       </c>
@@ -2690,37 +2690,37 @@
         <v>8</v>
       </c>
       <c r="M31" s="10"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O31" s="61"/>
-      <c r="P31" s="62"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="55"/>
       <c r="Q31" s="10"/>
-      <c r="R31" s="69" t="s">
+      <c r="R31" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S31" s="58"/>
-      <c r="T31" s="59"/>
+      <c r="S31" s="68"/>
+      <c r="T31" s="69"/>
       <c r="U31" s="10"/>
-      <c r="V31" s="60"/>
-      <c r="W31" s="61"/>
-      <c r="X31" s="62"/>
-      <c r="Y31" s="60"/>
-      <c r="Z31" s="61"/>
-      <c r="AA31" s="62"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="55"/>
+      <c r="Y31" s="65"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="55"/>
       <c r="AB31" s="33"/>
-      <c r="AC31" s="90" t="s">
+      <c r="AC31" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD31" s="59"/>
+      <c r="AD31" s="69"/>
       <c r="AE31" s="16"/>
       <c r="AF31" s="3"/>
     </row>
     <row r="32" spans="1:32" ht="12.75" customHeight="1">
       <c r="A32" s="28"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="62"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="29">
         <v>1</v>
       </c>
@@ -2746,37 +2746,37 @@
         <v>8</v>
       </c>
       <c r="M32" s="10"/>
-      <c r="N32" s="81" t="s">
+      <c r="N32" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O32" s="61"/>
-      <c r="P32" s="62"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="55"/>
       <c r="Q32" s="10"/>
-      <c r="R32" s="69" t="s">
+      <c r="R32" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="S32" s="58"/>
-      <c r="T32" s="59"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="69"/>
       <c r="U32" s="10"/>
-      <c r="V32" s="60"/>
-      <c r="W32" s="61"/>
-      <c r="X32" s="62"/>
-      <c r="Y32" s="60"/>
-      <c r="Z32" s="61"/>
-      <c r="AA32" s="62"/>
+      <c r="V32" s="65"/>
+      <c r="W32" s="54"/>
+      <c r="X32" s="55"/>
+      <c r="Y32" s="65"/>
+      <c r="Z32" s="54"/>
+      <c r="AA32" s="55"/>
       <c r="AB32" s="33"/>
-      <c r="AC32" s="90" t="s">
+      <c r="AC32" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="AD32" s="59"/>
+      <c r="AD32" s="69"/>
       <c r="AE32" s="16"/>
       <c r="AF32" s="3"/>
     </row>
     <row r="33" spans="1:32" ht="13.5" customHeight="1">
       <c r="A33" s="28"/>
-      <c r="B33" s="80"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="62"/>
+      <c r="B33" s="84"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="29">
         <v>1</v>
       </c>
@@ -2802,37 +2802,37 @@
         <v>8</v>
       </c>
       <c r="M33" s="10"/>
-      <c r="N33" s="81" t="s">
+      <c r="N33" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="O33" s="61"/>
-      <c r="P33" s="62"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="55"/>
       <c r="Q33" s="10"/>
-      <c r="R33" s="70" t="s">
+      <c r="R33" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="S33" s="55"/>
-      <c r="T33" s="56"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="52"/>
       <c r="U33" s="10"/>
-      <c r="V33" s="63"/>
-      <c r="W33" s="64"/>
-      <c r="X33" s="65"/>
-      <c r="Y33" s="63"/>
-      <c r="Z33" s="64"/>
-      <c r="AA33" s="65"/>
+      <c r="V33" s="66"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="63"/>
+      <c r="Y33" s="66"/>
+      <c r="Z33" s="62"/>
+      <c r="AA33" s="63"/>
       <c r="AB33" s="33"/>
-      <c r="AC33" s="91" t="s">
+      <c r="AC33" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="AD33" s="56"/>
+      <c r="AD33" s="52"/>
       <c r="AE33" s="16"/>
       <c r="AF33" s="3"/>
     </row>
     <row r="34" spans="1:32" ht="13.5" customHeight="1">
       <c r="A34" s="28"/>
-      <c r="B34" s="80"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="62"/>
+      <c r="B34" s="84"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="55"/>
       <c r="E34" s="29">
         <v>1</v>
       </c>
@@ -2858,9 +2858,9 @@
         <v>8</v>
       </c>
       <c r="M34" s="10"/>
-      <c r="N34" s="81"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="62"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="55"/>
       <c r="Q34" s="10"/>
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
@@ -2882,9 +2882,9 @@
     </row>
     <row r="35" spans="1:32" ht="12.75" customHeight="1">
       <c r="A35" s="28"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="62"/>
+      <c r="B35" s="84"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="55"/>
       <c r="E35" s="29">
         <v>1</v>
       </c>
@@ -2910,36 +2910,36 @@
         <v>8</v>
       </c>
       <c r="M35" s="10"/>
-      <c r="N35" s="81"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="62"/>
-      <c r="R35" s="50" t="s">
+      <c r="N35" s="53"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="55"/>
+      <c r="R35" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="S35" s="77"/>
-      <c r="T35" s="71" t="s">
+      <c r="S35" s="93"/>
+      <c r="T35" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="U35" s="67"/>
-      <c r="V35" s="67"/>
-      <c r="W35" s="67"/>
-      <c r="X35" s="67"/>
-      <c r="Y35" s="72"/>
+      <c r="U35" s="58"/>
+      <c r="V35" s="58"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="58"/>
+      <c r="Y35" s="87"/>
       <c r="Z35" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AA35" s="92"/>
-      <c r="AB35" s="67"/>
-      <c r="AC35" s="67"/>
-      <c r="AD35" s="68"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="58"/>
+      <c r="AC35" s="58"/>
+      <c r="AD35" s="59"/>
       <c r="AE35" s="16"/>
       <c r="AF35" s="3"/>
     </row>
     <row r="36" spans="1:32" ht="12.75" customHeight="1">
       <c r="A36" s="28"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="62"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="55"/>
       <c r="E36" s="29">
         <v>1</v>
       </c>
@@ -2965,36 +2965,36 @@
         <v>8</v>
       </c>
       <c r="M36" s="10"/>
-      <c r="N36" s="81"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="62"/>
-      <c r="R36" s="50" t="s">
+      <c r="N36" s="53"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="55"/>
+      <c r="R36" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="S36" s="77"/>
-      <c r="T36" s="73" t="s">
+      <c r="S36" s="93"/>
+      <c r="T36" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="U36" s="61"/>
-      <c r="V36" s="61"/>
-      <c r="W36" s="61"/>
-      <c r="X36" s="61"/>
-      <c r="Y36" s="74"/>
+      <c r="U36" s="54"/>
+      <c r="V36" s="54"/>
+      <c r="W36" s="54"/>
+      <c r="X36" s="54"/>
+      <c r="Y36" s="89"/>
       <c r="Z36" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="AA36" s="93"/>
-      <c r="AB36" s="61"/>
-      <c r="AC36" s="61"/>
-      <c r="AD36" s="62"/>
+      <c r="AA36" s="60"/>
+      <c r="AB36" s="54"/>
+      <c r="AC36" s="54"/>
+      <c r="AD36" s="55"/>
       <c r="AE36" s="16"/>
       <c r="AF36" s="3"/>
     </row>
     <row r="37" spans="1:32" ht="13.5" customHeight="1">
       <c r="A37" s="28"/>
-      <c r="B37" s="80"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="62"/>
+      <c r="B37" s="84"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="55"/>
       <c r="E37" s="29">
         <v>1</v>
       </c>
@@ -3020,34 +3020,34 @@
         <v>8</v>
       </c>
       <c r="M37" s="10"/>
-      <c r="N37" s="81"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="62"/>
-      <c r="R37" s="50" t="s">
+      <c r="N37" s="53"/>
+      <c r="O37" s="54"/>
+      <c r="P37" s="55"/>
+      <c r="R37" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="S37" s="77"/>
-      <c r="T37" s="75"/>
-      <c r="U37" s="64"/>
-      <c r="V37" s="64"/>
-      <c r="W37" s="64"/>
-      <c r="X37" s="64"/>
-      <c r="Y37" s="76"/>
+      <c r="S37" s="93"/>
+      <c r="T37" s="90"/>
+      <c r="U37" s="62"/>
+      <c r="V37" s="62"/>
+      <c r="W37" s="62"/>
+      <c r="X37" s="62"/>
+      <c r="Y37" s="91"/>
       <c r="Z37" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="AA37" s="94"/>
-      <c r="AB37" s="64"/>
-      <c r="AC37" s="64"/>
-      <c r="AD37" s="65"/>
+      <c r="AA37" s="61"/>
+      <c r="AB37" s="62"/>
+      <c r="AC37" s="62"/>
+      <c r="AD37" s="63"/>
       <c r="AE37" s="16"/>
       <c r="AF37" s="3"/>
     </row>
     <row r="38" spans="1:32" ht="13.5" customHeight="1">
       <c r="A38" s="28"/>
-      <c r="B38" s="80"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="62"/>
+      <c r="B38" s="84"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="55"/>
       <c r="E38" s="29">
         <v>1</v>
       </c>
@@ -3073,32 +3073,32 @@
         <v>8</v>
       </c>
       <c r="M38" s="10"/>
-      <c r="N38" s="81"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="62"/>
-      <c r="R38" s="50" t="s">
+      <c r="N38" s="53"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="55"/>
+      <c r="R38" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="S38" s="77"/>
-      <c r="T38" s="95"/>
-      <c r="U38" s="55"/>
-      <c r="V38" s="55"/>
-      <c r="W38" s="55"/>
-      <c r="X38" s="55"/>
-      <c r="Y38" s="55"/>
-      <c r="Z38" s="55"/>
-      <c r="AA38" s="55"/>
-      <c r="AB38" s="55"/>
-      <c r="AC38" s="55"/>
-      <c r="AD38" s="56"/>
+      <c r="S38" s="93"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="51"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="51"/>
+      <c r="Y38" s="51"/>
+      <c r="Z38" s="51"/>
+      <c r="AA38" s="51"/>
+      <c r="AB38" s="51"/>
+      <c r="AC38" s="51"/>
+      <c r="AD38" s="52"/>
       <c r="AE38" s="16"/>
       <c r="AF38" s="3"/>
     </row>
     <row r="39" spans="1:32" ht="12.75" customHeight="1">
       <c r="A39" s="28"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="62"/>
+      <c r="B39" s="84"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="55"/>
       <c r="E39" s="29">
         <v>1</v>
       </c>
@@ -3124,9 +3124,9 @@
         <v>8</v>
       </c>
       <c r="M39" s="10"/>
-      <c r="N39" s="81"/>
-      <c r="O39" s="61"/>
-      <c r="P39" s="62"/>
+      <c r="N39" s="53"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="55"/>
       <c r="Q39" s="10"/>
       <c r="S39" s="10"/>
       <c r="T39" s="10"/>
@@ -3147,9 +3147,9 @@
     </row>
     <row r="40" spans="1:32" ht="12.75" customHeight="1" thickBot="1">
       <c r="A40" s="28"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="55"/>
       <c r="E40" s="29">
         <v>1</v>
       </c>
@@ -3175,13 +3175,13 @@
         <v>8</v>
       </c>
       <c r="M40" s="10"/>
-      <c r="N40" s="81"/>
-      <c r="O40" s="61"/>
-      <c r="P40" s="62"/>
-      <c r="R40" s="50" t="s">
+      <c r="N40" s="53"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="55"/>
+      <c r="R40" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="S40" s="51"/>
+      <c r="S40" s="98"/>
       <c r="T40" s="36">
         <v>100</v>
       </c>
@@ -3220,9 +3220,9 @@
     </row>
     <row r="41" spans="1:32" ht="13.5" customHeight="1" thickBot="1">
       <c r="A41" s="28"/>
-      <c r="B41" s="80"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="62"/>
+      <c r="B41" s="84"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="55"/>
       <c r="E41" s="29">
         <v>1</v>
       </c>
@@ -3248,15 +3248,15 @@
         <v>8</v>
       </c>
       <c r="M41" s="10"/>
-      <c r="N41" s="81"/>
-      <c r="O41" s="61"/>
-      <c r="P41" s="62"/>
+      <c r="N41" s="53"/>
+      <c r="O41" s="54"/>
+      <c r="P41" s="55"/>
       <c r="Q41" s="31"/>
-      <c r="R41" s="108" t="s">
+      <c r="R41" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="S41" s="108"/>
-      <c r="T41" s="108"/>
+      <c r="S41" s="56"/>
+      <c r="T41" s="56"/>
       <c r="U41" s="10"/>
       <c r="V41" s="10"/>
       <c r="W41" s="10"/>
@@ -3272,9 +3272,9 @@
     </row>
     <row r="42" spans="1:32" ht="13.5" customHeight="1">
       <c r="A42" s="28"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="62"/>
+      <c r="B42" s="84"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="55"/>
       <c r="E42" s="29">
         <v>1</v>
       </c>
@@ -3300,9 +3300,9 @@
         <v>8</v>
       </c>
       <c r="M42" s="10"/>
-      <c r="N42" s="81"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="62"/>
+      <c r="N42" s="53"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="55"/>
       <c r="Q42" s="38"/>
       <c r="R42" s="100"/>
       <c r="S42" s="101"/>
@@ -3322,9 +3322,9 @@
     </row>
     <row r="43" spans="1:32" ht="12.75" customHeight="1">
       <c r="A43" s="28"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="62"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="55"/>
       <c r="E43" s="29">
         <v>1</v>
       </c>
@@ -3350,31 +3350,31 @@
         <v>8</v>
       </c>
       <c r="M43" s="10"/>
-      <c r="N43" s="81"/>
-      <c r="O43" s="61"/>
-      <c r="P43" s="62"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="54"/>
+      <c r="P43" s="55"/>
       <c r="Q43" s="40"/>
       <c r="R43" s="103"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="99"/>
-      <c r="V43" s="99"/>
-      <c r="W43" s="99"/>
-      <c r="X43" s="99"/>
-      <c r="Y43" s="99"/>
-      <c r="Z43" s="99"/>
-      <c r="AA43" s="99"/>
-      <c r="AB43" s="99"/>
-      <c r="AC43" s="99"/>
-      <c r="AD43" s="104"/>
+      <c r="S43" s="104"/>
+      <c r="T43" s="104"/>
+      <c r="U43" s="104"/>
+      <c r="V43" s="104"/>
+      <c r="W43" s="104"/>
+      <c r="X43" s="104"/>
+      <c r="Y43" s="104"/>
+      <c r="Z43" s="104"/>
+      <c r="AA43" s="104"/>
+      <c r="AB43" s="104"/>
+      <c r="AC43" s="104"/>
+      <c r="AD43" s="105"/>
       <c r="AE43" s="16"/>
       <c r="AF43" s="3"/>
     </row>
     <row r="44" spans="1:32" ht="12.75" customHeight="1">
       <c r="A44" s="28"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="62"/>
+      <c r="B44" s="84"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="55"/>
       <c r="E44" s="29">
         <v>1</v>
       </c>
@@ -3400,31 +3400,31 @@
         <v>8</v>
       </c>
       <c r="M44" s="10"/>
-      <c r="N44" s="81"/>
-      <c r="O44" s="61"/>
-      <c r="P44" s="62"/>
+      <c r="N44" s="53"/>
+      <c r="O44" s="54"/>
+      <c r="P44" s="55"/>
       <c r="Q44" s="40"/>
       <c r="R44" s="103"/>
-      <c r="S44" s="99"/>
-      <c r="T44" s="99"/>
-      <c r="U44" s="99"/>
-      <c r="V44" s="99"/>
-      <c r="W44" s="99"/>
-      <c r="X44" s="99"/>
-      <c r="Y44" s="99"/>
-      <c r="Z44" s="99"/>
-      <c r="AA44" s="99"/>
-      <c r="AB44" s="99"/>
-      <c r="AC44" s="99"/>
-      <c r="AD44" s="104"/>
+      <c r="S44" s="104"/>
+      <c r="T44" s="104"/>
+      <c r="U44" s="104"/>
+      <c r="V44" s="104"/>
+      <c r="W44" s="104"/>
+      <c r="X44" s="104"/>
+      <c r="Y44" s="104"/>
+      <c r="Z44" s="104"/>
+      <c r="AA44" s="104"/>
+      <c r="AB44" s="104"/>
+      <c r="AC44" s="104"/>
+      <c r="AD44" s="105"/>
       <c r="AE44" s="16"/>
       <c r="AF44" s="3"/>
     </row>
     <row r="45" spans="1:32" ht="12.75" customHeight="1">
       <c r="A45" s="28"/>
-      <c r="B45" s="80"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="62"/>
+      <c r="B45" s="84"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="55"/>
       <c r="E45" s="41">
         <v>1</v>
       </c>
@@ -3450,31 +3450,31 @@
         <v>8</v>
       </c>
       <c r="M45" s="10"/>
-      <c r="N45" s="81"/>
-      <c r="O45" s="61"/>
-      <c r="P45" s="62"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="55"/>
       <c r="Q45" s="40"/>
       <c r="R45" s="103"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="99"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="99"/>
-      <c r="X45" s="99"/>
-      <c r="Y45" s="99"/>
-      <c r="Z45" s="99"/>
-      <c r="AA45" s="99"/>
-      <c r="AB45" s="99"/>
-      <c r="AC45" s="99"/>
-      <c r="AD45" s="104"/>
+      <c r="S45" s="104"/>
+      <c r="T45" s="104"/>
+      <c r="U45" s="104"/>
+      <c r="V45" s="104"/>
+      <c r="W45" s="104"/>
+      <c r="X45" s="104"/>
+      <c r="Y45" s="104"/>
+      <c r="Z45" s="104"/>
+      <c r="AA45" s="104"/>
+      <c r="AB45" s="104"/>
+      <c r="AC45" s="104"/>
+      <c r="AD45" s="105"/>
       <c r="AE45" s="16"/>
       <c r="AF45" s="3"/>
     </row>
     <row r="46" spans="1:32" ht="12.75" customHeight="1">
       <c r="A46" s="28"/>
-      <c r="B46" s="80"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="62"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="55"/>
       <c r="E46" s="41">
         <v>1</v>
       </c>
@@ -3500,31 +3500,31 @@
         <v>8</v>
       </c>
       <c r="M46" s="10"/>
-      <c r="N46" s="81"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="62"/>
+      <c r="N46" s="53"/>
+      <c r="O46" s="54"/>
+      <c r="P46" s="55"/>
       <c r="Q46" s="40"/>
       <c r="R46" s="103"/>
-      <c r="S46" s="99"/>
-      <c r="T46" s="99"/>
-      <c r="U46" s="99"/>
-      <c r="V46" s="99"/>
-      <c r="W46" s="99"/>
-      <c r="X46" s="99"/>
-      <c r="Y46" s="99"/>
-      <c r="Z46" s="99"/>
-      <c r="AA46" s="99"/>
-      <c r="AB46" s="99"/>
-      <c r="AC46" s="99"/>
-      <c r="AD46" s="104"/>
+      <c r="S46" s="104"/>
+      <c r="T46" s="104"/>
+      <c r="U46" s="104"/>
+      <c r="V46" s="104"/>
+      <c r="W46" s="104"/>
+      <c r="X46" s="104"/>
+      <c r="Y46" s="104"/>
+      <c r="Z46" s="104"/>
+      <c r="AA46" s="104"/>
+      <c r="AB46" s="104"/>
+      <c r="AC46" s="104"/>
+      <c r="AD46" s="105"/>
       <c r="AE46" s="16"/>
       <c r="AF46" s="3"/>
     </row>
     <row r="47" spans="1:32" ht="13.5" customHeight="1">
       <c r="A47" s="28"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="62"/>
+      <c r="B47" s="84"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="55"/>
       <c r="E47" s="41">
         <v>1</v>
       </c>
@@ -3550,31 +3550,31 @@
         <v>8</v>
       </c>
       <c r="M47" s="10"/>
-      <c r="N47" s="81"/>
-      <c r="O47" s="61"/>
-      <c r="P47" s="62"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="55"/>
       <c r="Q47" s="40"/>
       <c r="R47" s="103"/>
-      <c r="S47" s="99"/>
-      <c r="T47" s="99"/>
-      <c r="U47" s="99"/>
-      <c r="V47" s="99"/>
-      <c r="W47" s="99"/>
-      <c r="X47" s="99"/>
-      <c r="Y47" s="99"/>
-      <c r="Z47" s="99"/>
-      <c r="AA47" s="99"/>
-      <c r="AB47" s="99"/>
-      <c r="AC47" s="99"/>
-      <c r="AD47" s="104"/>
+      <c r="S47" s="104"/>
+      <c r="T47" s="104"/>
+      <c r="U47" s="104"/>
+      <c r="V47" s="104"/>
+      <c r="W47" s="104"/>
+      <c r="X47" s="104"/>
+      <c r="Y47" s="104"/>
+      <c r="Z47" s="104"/>
+      <c r="AA47" s="104"/>
+      <c r="AB47" s="104"/>
+      <c r="AC47" s="104"/>
+      <c r="AD47" s="105"/>
       <c r="AE47" s="16"/>
       <c r="AF47" s="3"/>
     </row>
     <row r="48" spans="1:32" ht="13.5" customHeight="1">
       <c r="A48" s="28"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="62"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="55"/>
       <c r="E48" s="41">
         <v>1</v>
       </c>
@@ -3600,31 +3600,31 @@
         <v>8</v>
       </c>
       <c r="M48" s="10"/>
-      <c r="N48" s="81"/>
-      <c r="O48" s="61"/>
-      <c r="P48" s="62"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="55"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="103"/>
-      <c r="S48" s="99"/>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="99"/>
-      <c r="W48" s="99"/>
-      <c r="X48" s="99"/>
-      <c r="Y48" s="99"/>
-      <c r="Z48" s="99"/>
-      <c r="AA48" s="99"/>
-      <c r="AB48" s="99"/>
-      <c r="AC48" s="99"/>
-      <c r="AD48" s="104"/>
+      <c r="S48" s="104"/>
+      <c r="T48" s="104"/>
+      <c r="U48" s="104"/>
+      <c r="V48" s="104"/>
+      <c r="W48" s="104"/>
+      <c r="X48" s="104"/>
+      <c r="Y48" s="104"/>
+      <c r="Z48" s="104"/>
+      <c r="AA48" s="104"/>
+      <c r="AB48" s="104"/>
+      <c r="AC48" s="104"/>
+      <c r="AD48" s="105"/>
       <c r="AE48" s="16"/>
       <c r="AF48" s="3"/>
     </row>
     <row r="49" spans="1:32" ht="12.75" customHeight="1">
       <c r="A49" s="28"/>
-      <c r="B49" s="80"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="62"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="55"/>
       <c r="E49" s="41">
         <v>1</v>
       </c>
@@ -3650,31 +3650,31 @@
         <v>8</v>
       </c>
       <c r="M49" s="10"/>
-      <c r="N49" s="81"/>
-      <c r="O49" s="61"/>
-      <c r="P49" s="62"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="55"/>
       <c r="Q49" s="10"/>
       <c r="R49" s="103"/>
-      <c r="S49" s="99"/>
-      <c r="T49" s="99"/>
-      <c r="U49" s="99"/>
-      <c r="V49" s="99"/>
-      <c r="W49" s="99"/>
-      <c r="X49" s="99"/>
-      <c r="Y49" s="99"/>
-      <c r="Z49" s="99"/>
-      <c r="AA49" s="99"/>
-      <c r="AB49" s="99"/>
-      <c r="AC49" s="99"/>
-      <c r="AD49" s="104"/>
+      <c r="S49" s="104"/>
+      <c r="T49" s="104"/>
+      <c r="U49" s="104"/>
+      <c r="V49" s="104"/>
+      <c r="W49" s="104"/>
+      <c r="X49" s="104"/>
+      <c r="Y49" s="104"/>
+      <c r="Z49" s="104"/>
+      <c r="AA49" s="104"/>
+      <c r="AB49" s="104"/>
+      <c r="AC49" s="104"/>
+      <c r="AD49" s="105"/>
       <c r="AE49" s="16"/>
       <c r="AF49" s="3"/>
     </row>
     <row r="50" spans="1:32" ht="12.75" customHeight="1">
       <c r="A50" s="28"/>
-      <c r="B50" s="80"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="62"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="55"/>
       <c r="E50" s="41">
         <v>1</v>
       </c>
@@ -3700,31 +3700,31 @@
         <v>8</v>
       </c>
       <c r="M50" s="10"/>
-      <c r="N50" s="81"/>
-      <c r="O50" s="61"/>
-      <c r="P50" s="62"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="55"/>
       <c r="Q50" s="44"/>
       <c r="R50" s="103"/>
-      <c r="S50" s="99"/>
-      <c r="T50" s="99"/>
-      <c r="U50" s="99"/>
-      <c r="V50" s="99"/>
-      <c r="W50" s="99"/>
-      <c r="X50" s="99"/>
-      <c r="Y50" s="99"/>
-      <c r="Z50" s="99"/>
-      <c r="AA50" s="99"/>
-      <c r="AB50" s="99"/>
-      <c r="AC50" s="99"/>
-      <c r="AD50" s="104"/>
+      <c r="S50" s="104"/>
+      <c r="T50" s="104"/>
+      <c r="U50" s="104"/>
+      <c r="V50" s="104"/>
+      <c r="W50" s="104"/>
+      <c r="X50" s="104"/>
+      <c r="Y50" s="104"/>
+      <c r="Z50" s="104"/>
+      <c r="AA50" s="104"/>
+      <c r="AB50" s="104"/>
+      <c r="AC50" s="104"/>
+      <c r="AD50" s="105"/>
       <c r="AE50" s="16"/>
       <c r="AF50" s="3"/>
     </row>
     <row r="51" spans="1:32" ht="12.75" customHeight="1">
       <c r="A51" s="28"/>
-      <c r="B51" s="80"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="62"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="55"/>
       <c r="E51" s="29">
         <v>1</v>
       </c>
@@ -3750,31 +3750,31 @@
         <v>8</v>
       </c>
       <c r="M51" s="10"/>
-      <c r="N51" s="81"/>
-      <c r="O51" s="61"/>
-      <c r="P51" s="62"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="54"/>
+      <c r="P51" s="55"/>
       <c r="Q51" s="44"/>
       <c r="R51" s="103"/>
-      <c r="S51" s="99"/>
-      <c r="T51" s="99"/>
-      <c r="U51" s="99"/>
-      <c r="V51" s="99"/>
-      <c r="W51" s="99"/>
-      <c r="X51" s="99"/>
-      <c r="Y51" s="99"/>
-      <c r="Z51" s="99"/>
-      <c r="AA51" s="99"/>
-      <c r="AB51" s="99"/>
-      <c r="AC51" s="99"/>
-      <c r="AD51" s="104"/>
+      <c r="S51" s="104"/>
+      <c r="T51" s="104"/>
+      <c r="U51" s="104"/>
+      <c r="V51" s="104"/>
+      <c r="W51" s="104"/>
+      <c r="X51" s="104"/>
+      <c r="Y51" s="104"/>
+      <c r="Z51" s="104"/>
+      <c r="AA51" s="104"/>
+      <c r="AB51" s="104"/>
+      <c r="AC51" s="104"/>
+      <c r="AD51" s="105"/>
       <c r="AE51" s="16"/>
       <c r="AF51" s="3"/>
     </row>
     <row r="52" spans="1:32" ht="12.75" customHeight="1">
       <c r="A52" s="28"/>
-      <c r="B52" s="80"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="62"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="55"/>
       <c r="E52" s="29">
         <v>1</v>
       </c>
@@ -3800,31 +3800,31 @@
         <v>8</v>
       </c>
       <c r="M52" s="10"/>
-      <c r="N52" s="81"/>
-      <c r="O52" s="61"/>
-      <c r="P52" s="62"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="55"/>
       <c r="Q52" s="44"/>
       <c r="R52" s="103"/>
-      <c r="S52" s="99"/>
-      <c r="T52" s="99"/>
-      <c r="U52" s="99"/>
-      <c r="V52" s="99"/>
-      <c r="W52" s="99"/>
-      <c r="X52" s="99"/>
-      <c r="Y52" s="99"/>
-      <c r="Z52" s="99"/>
-      <c r="AA52" s="99"/>
-      <c r="AB52" s="99"/>
-      <c r="AC52" s="99"/>
-      <c r="AD52" s="104"/>
+      <c r="S52" s="104"/>
+      <c r="T52" s="104"/>
+      <c r="U52" s="104"/>
+      <c r="V52" s="104"/>
+      <c r="W52" s="104"/>
+      <c r="X52" s="104"/>
+      <c r="Y52" s="104"/>
+      <c r="Z52" s="104"/>
+      <c r="AA52" s="104"/>
+      <c r="AB52" s="104"/>
+      <c r="AC52" s="104"/>
+      <c r="AD52" s="105"/>
       <c r="AE52" s="16"/>
       <c r="AF52" s="3"/>
     </row>
     <row r="53" spans="1:32" ht="13.5" customHeight="1" thickBot="1">
       <c r="A53" s="28"/>
-      <c r="B53" s="79"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="56"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="52"/>
       <c r="E53" s="45">
         <v>1</v>
       </c>
@@ -3850,23 +3850,23 @@
         <v>8</v>
       </c>
       <c r="M53" s="10"/>
-      <c r="N53" s="87"/>
-      <c r="O53" s="55"/>
-      <c r="P53" s="56"/>
+      <c r="N53" s="79"/>
+      <c r="O53" s="51"/>
+      <c r="P53" s="52"/>
       <c r="Q53" s="40"/>
-      <c r="R53" s="105"/>
-      <c r="S53" s="106"/>
-      <c r="T53" s="106"/>
-      <c r="U53" s="106"/>
-      <c r="V53" s="106"/>
-      <c r="W53" s="106"/>
-      <c r="X53" s="106"/>
-      <c r="Y53" s="106"/>
-      <c r="Z53" s="106"/>
-      <c r="AA53" s="106"/>
-      <c r="AB53" s="106"/>
-      <c r="AC53" s="106"/>
-      <c r="AD53" s="107"/>
+      <c r="R53" s="106"/>
+      <c r="S53" s="107"/>
+      <c r="T53" s="107"/>
+      <c r="U53" s="107"/>
+      <c r="V53" s="107"/>
+      <c r="W53" s="107"/>
+      <c r="X53" s="107"/>
+      <c r="Y53" s="107"/>
+      <c r="Z53" s="107"/>
+      <c r="AA53" s="107"/>
+      <c r="AB53" s="107"/>
+      <c r="AC53" s="107"/>
+      <c r="AD53" s="108"/>
       <c r="AE53" s="16"/>
       <c r="AF53" s="3"/>
     </row>
@@ -3905,37 +3905,37 @@
       <c r="AF54" s="3"/>
     </row>
     <row r="55" spans="1:32" ht="24" customHeight="1">
-      <c r="A55" s="98"/>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
-      <c r="E55" s="55"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="55"/>
-      <c r="H55" s="55"/>
-      <c r="I55" s="55"/>
-      <c r="J55" s="55"/>
-      <c r="K55" s="55"/>
-      <c r="L55" s="55"/>
-      <c r="M55" s="55"/>
-      <c r="N55" s="55"/>
-      <c r="O55" s="55"/>
-      <c r="P55" s="55"/>
-      <c r="Q55" s="55"/>
-      <c r="R55" s="55"/>
-      <c r="S55" s="55"/>
-      <c r="T55" s="55"/>
-      <c r="U55" s="55"/>
-      <c r="V55" s="55"/>
-      <c r="W55" s="55"/>
-      <c r="X55" s="55"/>
-      <c r="Y55" s="55"/>
-      <c r="Z55" s="55"/>
-      <c r="AA55" s="55"/>
-      <c r="AB55" s="55"/>
-      <c r="AC55" s="55"/>
-      <c r="AD55" s="55"/>
-      <c r="AE55" s="56"/>
+      <c r="A55" s="50"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="51"/>
+      <c r="M55" s="51"/>
+      <c r="N55" s="51"/>
+      <c r="O55" s="51"/>
+      <c r="P55" s="51"/>
+      <c r="Q55" s="51"/>
+      <c r="R55" s="51"/>
+      <c r="S55" s="51"/>
+      <c r="T55" s="51"/>
+      <c r="U55" s="51"/>
+      <c r="V55" s="51"/>
+      <c r="W55" s="51"/>
+      <c r="X55" s="51"/>
+      <c r="Y55" s="51"/>
+      <c r="Z55" s="51"/>
+      <c r="AA55" s="51"/>
+      <c r="AB55" s="51"/>
+      <c r="AC55" s="51"/>
+      <c r="AD55" s="51"/>
+      <c r="AE55" s="52"/>
       <c r="AF55" s="3"/>
     </row>
     <row r="56" spans="1:32" ht="12.75" customHeight="1">
@@ -11485,35 +11485,145 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="A55:AE55"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R42:AD53"/>
-    <mergeCell ref="R41:T41"/>
-    <mergeCell ref="AA35:AD35"/>
-    <mergeCell ref="AA36:AD36"/>
-    <mergeCell ref="AA37:AD37"/>
-    <mergeCell ref="T38:AD38"/>
-    <mergeCell ref="V22:AA22"/>
-    <mergeCell ref="V23:AA23"/>
-    <mergeCell ref="V24:AA24"/>
-    <mergeCell ref="Y26:AA26"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="AC26:AD26"/>
-    <mergeCell ref="Y32:AA32"/>
-    <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="AC29:AD29"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="AC30:AD30"/>
-    <mergeCell ref="Y31:AA31"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="AC32:AD32"/>
-    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="S9:U9"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="S13:U13"/>
+    <mergeCell ref="S14:U14"/>
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="S16:U16"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="R23:T23"/>
+    <mergeCell ref="R24:T24"/>
+    <mergeCell ref="V28:X28"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="R25:T25"/>
+    <mergeCell ref="R26:T26"/>
+    <mergeCell ref="V26:X26"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="V27:X27"/>
+    <mergeCell ref="R28:T28"/>
+    <mergeCell ref="R29:T29"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="V30:X30"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="V31:X31"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="V32:X32"/>
+    <mergeCell ref="V33:X33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="T35:Y35"/>
+    <mergeCell ref="T36:Y36"/>
+    <mergeCell ref="T37:Y37"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="B12:L12"/>
+    <mergeCell ref="B13:L13"/>
+    <mergeCell ref="B14:L14"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="W5:Z5"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="W6:Z6"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="AA7:AD7"/>
+    <mergeCell ref="B8:L8"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="W7:Z7"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="V9:AA9"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="V19:AA19"/>
+    <mergeCell ref="AB19:AD19"/>
+    <mergeCell ref="V20:AA20"/>
+    <mergeCell ref="V21:AA21"/>
+    <mergeCell ref="V12:AA12"/>
+    <mergeCell ref="AB12:AD12"/>
+    <mergeCell ref="V13:AA13"/>
+    <mergeCell ref="AB13:AD13"/>
+    <mergeCell ref="AB14:AD14"/>
+    <mergeCell ref="V14:AA14"/>
+    <mergeCell ref="V15:AA15"/>
+    <mergeCell ref="AB15:AD15"/>
+    <mergeCell ref="V16:AA16"/>
+    <mergeCell ref="AB16:AD16"/>
     <mergeCell ref="B10:L10"/>
     <mergeCell ref="S10:U10"/>
     <mergeCell ref="V10:AA10"/>
@@ -11538,29 +11648,35 @@
     <mergeCell ref="V18:AA18"/>
     <mergeCell ref="AB18:AD18"/>
     <mergeCell ref="R19:T19"/>
-    <mergeCell ref="V19:AA19"/>
-    <mergeCell ref="AB19:AD19"/>
-    <mergeCell ref="V20:AA20"/>
-    <mergeCell ref="V21:AA21"/>
-    <mergeCell ref="V12:AA12"/>
-    <mergeCell ref="AB12:AD12"/>
-    <mergeCell ref="V13:AA13"/>
-    <mergeCell ref="AB13:AD13"/>
-    <mergeCell ref="AB14:AD14"/>
-    <mergeCell ref="V14:AA14"/>
-    <mergeCell ref="V15:AA15"/>
-    <mergeCell ref="AB15:AD15"/>
-    <mergeCell ref="V16:AA16"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Y33:AA33"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="Y30:AA30"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="Y31:AA31"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="AC32:AD32"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="V22:AA22"/>
+    <mergeCell ref="V23:AA23"/>
+    <mergeCell ref="V24:AA24"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="Y32:AA32"/>
+    <mergeCell ref="A55:AE55"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R42:AD53"/>
+    <mergeCell ref="R41:T41"/>
+    <mergeCell ref="AA35:AD35"/>
+    <mergeCell ref="AA36:AD36"/>
+    <mergeCell ref="AA37:AD37"/>
+    <mergeCell ref="T38:AD38"/>
     <mergeCell ref="N38:P38"/>
     <mergeCell ref="N39:P39"/>
     <mergeCell ref="N50:P50"/>
@@ -11573,123 +11689,7 @@
     <mergeCell ref="N48:P48"/>
     <mergeCell ref="N49:P49"/>
     <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="B5:L5"/>
-    <mergeCell ref="B6:L6"/>
-    <mergeCell ref="W6:Z6"/>
-    <mergeCell ref="B7:L7"/>
-    <mergeCell ref="AA7:AD7"/>
-    <mergeCell ref="B8:L8"/>
-    <mergeCell ref="B9:L9"/>
-    <mergeCell ref="W7:Z7"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="V9:AA9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="D3:L3"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="W4:Z4"/>
-    <mergeCell ref="W5:Z5"/>
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="N3:P3"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="T35:Y35"/>
-    <mergeCell ref="T36:Y36"/>
-    <mergeCell ref="T37:Y37"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="B12:L12"/>
-    <mergeCell ref="B13:L13"/>
-    <mergeCell ref="B14:L14"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="V30:X30"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="V31:X31"/>
-    <mergeCell ref="R32:T32"/>
-    <mergeCell ref="V32:X32"/>
-    <mergeCell ref="V33:X33"/>
-    <mergeCell ref="R33:T33"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="S9:U9"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="S13:U13"/>
-    <mergeCell ref="S14:U14"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="S16:U16"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="R22:T22"/>
-    <mergeCell ref="R23:T23"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="V28:X28"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="R25:T25"/>
-    <mergeCell ref="R26:T26"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="R27:T27"/>
-    <mergeCell ref="V27:X27"/>
-    <mergeCell ref="R28:T28"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait"/>
